--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_他素案への追加候補の対応表_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_他素案への追加候補の対応表_20261020.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前回計画の目標値" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'対応表'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'対応表'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>他素案は題名の改正を正しく書き、法律にない語（「医療的ケア者」）も使っていない。成人期への接続の根拠条項だけを補う</t>
+          <t>他素案は題名の改正を正しく書いている。なお法律の語は「医療的ケア児等」、基本指針の改正案は「医療的ケア者」も定義して用いる。成人期への接続の根拠条項だけを補う</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1415,8 +1415,428 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
     </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>第3部第6章冒頭　見込量の定め方</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>―（当方素案にも無い）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>生活介護・就労継続支援Ｂ型・施設入所支援の見込量は継続入所者の数を除いて設定したこと（本町の該当者数。0人なら「該当なし」）</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>告示 第三の二の2（一）が「ものとする」とする定め方。継続入所者＝旧指定知的障害児施設等から引き続き入所している18歳以上の方（論点漏れの点検 R1）</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>第3部第7章1　障がい児通所支援</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>―（当方素案にも無い）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>見込量は保育所等における障がい児の受入れ体制の整備状況を踏まえて設定したこと</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>告示 第三の二の2（一）が「ものとする」とする定め方。町の保育部局に受入れの状況を確かめる（論点漏れの点検 R2）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>第3部第6章冒頭　見込量の定め方（別表第五）</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>内部検討（判定未了）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>別表第五（地域差の是正）の適用判定。本町が全部過疎か一部過疎か、6サービスの利用者割合が上位25％に入るか</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全部過疎なら対象外。対象なら6サービスの算定方法が定まる。該当・非該当のいずれでも判定を1行書く。過疎区分の確認が先（論点漏れの点検 R3）</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>第3部第5章8　質を向上させるための取組に係る体制の構築</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>第3部第1章（成果目標）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>情報公表制度の公表率・更新率100％を町の【目標値】から外し、県の目標として参考に掲げる。町は事業所への周知・働きかけを活動として書く</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>置換</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>告示 第二の八は「各都道府県、政令市又は中核市における管内事業所の」目標とする。町は指定権者でない（論点漏れの点検 R4）</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>第2部第7章1　意思決定支援及び相談支援体制の充実</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>第2部第2章（意思決定支援）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>意思決定支援ガイドライン（第2版）の名指しと、相談支援専門員等が県の研修を受けること</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>補記</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>告示が名指しするガイドライン。第2版は意思形成・意思表明・意思実現の3段階（論点漏れの点検 R5）</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>第3部第6章　各サービスの見込量の表（重度障がい者の内数）</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>重度障がい者の内数をサービスごと（生活介護・短期入所・共同生活援助）の行として置く</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>補記</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>他素案は区分ごとの人数の表のみ。告示 別表第一はサービスごとの内数を求める（論点漏れの点検 R6）</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>第3部第4章4（1）／第7章3　医療的ケア</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>第2部第6章3</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>県が設ける医療的ケア児等支援地域協議会との関係、学齢期から成人期への引継ぎの協議、センターの「医療的ケア児等支援センター」への改称</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>基本指針の改正案（第21回、令和8年8月19日）。告示後に最終照合する（論点漏れの点検 R7）</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>第1部第2章2　年次の点検評価の方法</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>第1部第1章7</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>実態調査及びPDCAマニュアル（令和8年8月改定）と福島県通知（8生福第2646号、令和8年8月24日）を点検の拠り所として挙げる</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>補記</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>他素案は独自に点検項目を立てており、国のマニュアルとの関係が書かれていない（論点漏れの点検 R8）</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>第3部第6章2　日中活動系サービス（就労移行支援）</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>見込量の勘案事項に復職を希望する休職者等を加える</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>補記</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>告示 別表第一（就労移行支援）の勘案事項（論点漏れの点検 R9）</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>第1部第1章1／第2部第2章3　成年後見制度</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>民法等の一部を改正する法律の法律番号（令和8年法律第45号）</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>補記</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>他素案は法律名のみ（論点漏れの点検 R10）</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J22"/>
+  <autoFilter ref="A1:J32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_他素案への追加候補の対応表_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_他素案への追加候補の対応表_20261020.xlsx
@@ -992,7 +992,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="90" customHeight="1">
@@ -1076,7 +1080,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="90" customHeight="1">
@@ -1118,7 +1126,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="90" customHeight="1">
@@ -1202,7 +1214,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="90" customHeight="1">
@@ -1328,7 +1344,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="90" customHeight="1">
@@ -1454,7 +1474,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="90" customHeight="1">
@@ -1496,7 +1520,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="90" customHeight="1">
@@ -1538,7 +1566,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="90" customHeight="1">
@@ -1580,7 +1612,11 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>済（変更履歴付き）</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="90" customHeight="1">

--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_他素案への追加候補の対応表_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_他素案への追加候補の対応表_20261020.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>他素案は「整合性と調和を図り」とし、条項を引いていない。障がい2法の語は「調和」であり「整合性の確保」ではない。当方は一度「第5項」と誤り、法令APIの条文で第7項に訂正した経緯がある</t>
+          <t>他素案は「整合性と調和を図り」とし、条項を引いていない。障がい2法の語は「調和」であり「整合性の確保」ではない。調和の規定は第7項（法令APIの条文で確認）</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
